--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/01. Báo giá sửa chữa/BG_AnhTuanBG_260826.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/01. Báo giá sửa chữa/BG_AnhTuanBG_260826.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 09\01. Báo giá sửa chữa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F7CD97-1321-480E-A821-C65BA5AFB2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0357C468-ECB7-496C-8FB0-C7E1B7303025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,7 +128,7 @@
     <t>Khay Nano SIM</t>
   </si>
   <si>
-    <t>Báo giá khách đã đồng ý sủa chữa, công nợ ghi KD. Lực</t>
+    <t>Báo giá tháng 08 đẩy qua tháng 09, báo giá khách đã đồng ý sủa chữa, công nợ ghi KD</t>
   </si>
 </sst>
 </file>
@@ -485,6 +485,18 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -562,18 +574,6 @@
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -956,82 +956,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33"/>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="39" t="s">
+      <c r="A1" s="37"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="42" t="s">
+      <c r="A2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="44"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="33"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="45" t="s">
+      <c r="A3" s="37"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="47"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="48" t="s">
+      <c r="A4" s="40"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="50"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="53"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="57"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="12"/>
@@ -1042,11 +1042,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -1056,11 +1056,11 @@
       <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
       <c r="D8" s="23"/>
       <c r="E8" s="23"/>
       <c r="F8" s="23" t="s">
@@ -1073,11 +1073,11 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
       <c r="F9" s="23"/>
@@ -1197,17 +1197,17 @@
       <c r="AA12" s="2"/>
     </row>
     <row r="13" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="58" t="s">
+      <c r="A13" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="60"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="34"/>
       <c r="J13" s="19">
         <f>SUM(J11:J12)</f>
         <v>100000</v>
@@ -1229,37 +1229,37 @@
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="57" t="s">
+      <c r="A15" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="57" t="s">
+      <c r="G15" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
       <c r="AA16" s="2"/>
     </row>
     <row r="17" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1317,20 +1317,20 @@
       <c r="AA20" s="2"/>
     </row>
     <row r="21" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="32" t="s">
+      <c r="G21" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
       <c r="K21" s="9"/>
       <c r="AA21" s="2"/>
     </row>
@@ -1408,6 +1408,16 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="17">
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A1:D4"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="E4:J4"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="G15:J15"/>
@@ -1415,16 +1425,6 @@
     <mergeCell ref="G21:J21"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A1:D4"/>
-    <mergeCell ref="E1:J1"/>
-    <mergeCell ref="E2:J2"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/01. Báo giá sửa chữa/BG_AnhTuanBG_260826.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/01. Báo giá sửa chữa/BG_AnhTuanBG_260826.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 09\01. Báo giá sửa chữa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0357C468-ECB7-496C-8FB0-C7E1B7303025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7460BCEC-E60B-4B03-B9E6-A8A9B31D330E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,7 +128,7 @@
     <t>Khay Nano SIM</t>
   </si>
   <si>
-    <t>Báo giá tháng 08 đẩy qua tháng 09, báo giá khách đã đồng ý sủa chữa, công nợ ghi KD</t>
+    <t>Báo giá tháng 08 đẩy qua tháng 09, báo giá khách đã đồng ý sửa chữa, công nợ ghi KD</t>
   </si>
 </sst>
 </file>
@@ -485,6 +485,78 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -502,78 +574,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1012,26 +1012,26 @@
       <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="57"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="33"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="12"/>
@@ -1042,11 +1042,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -1056,11 +1056,11 @@
       <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
       <c r="D8" s="23"/>
       <c r="E8" s="23"/>
       <c r="F8" s="23" t="s">
@@ -1073,11 +1073,11 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
       <c r="F9" s="23"/>
@@ -1197,17 +1197,17 @@
       <c r="AA12" s="2"/>
     </row>
     <row r="13" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="34"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="58"/>
       <c r="J13" s="19">
         <f>SUM(J11:J12)</f>
         <v>100000</v>
@@ -1229,37 +1229,37 @@
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="55"/>
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="35" t="s">
+      <c r="A16" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
-      <c r="G16" s="35" t="s">
+      <c r="G16" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="59"/>
       <c r="AA16" s="2"/>
     </row>
     <row r="17" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1317,20 +1317,20 @@
       <c r="AA20" s="2"/>
     </row>
     <row r="21" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="36" t="s">
+      <c r="G21" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
       <c r="K21" s="9"/>
       <c r="AA21" s="2"/>
     </row>
@@ -1408,16 +1408,6 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="17">
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A1:D4"/>
-    <mergeCell ref="E1:J1"/>
-    <mergeCell ref="E2:J2"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="E4:J4"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="G15:J15"/>
@@ -1425,6 +1415,16 @@
     <mergeCell ref="G21:J21"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A1:D4"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
